--- a/backtest_runs/20260410_193731/filter/BBFL/BBFL.xlsx
+++ b/backtest_runs/20260410_193731/filter/BBFL/BBFL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-2102.159999999994</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>104038.36</v>
@@ -679,7 +679,7 @@
         <v>-10787.4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>93250.96000000001</v>
@@ -771,7 +771,7 @@
         <v>-1631.93999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>95408.44</v>
@@ -817,7 +817,7 @@
         <v>-829.8000000000118</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>94578.64</v>
@@ -909,7 +909,7 @@
         <v>-1604.279999999995</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>93942.46000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-2102.159999999994</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>94274.38</v>
@@ -1185,7 +1185,7 @@
         <v>-3014.94000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>93278.62</v>
@@ -1277,7 +1277,7 @@
         <v>-4840.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>88797.70000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-248.9400000000094</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>88548.75999999999</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>88548.75999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-1493.639999999998</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>87055.12</v>
@@ -1645,7 +1645,7 @@
         <v>-2987.279999999995</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>94163.74000000001</v>
